--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFVitalsPosition</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPosition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_VitalsPosition</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
+    <t>Navigate to the [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include from 120.5-5" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -35,28 +36,28 @@
     <t>Name</t>
   </si>
   <si>
+    <t>VSVFVitalsPosition</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>VF_VitalsPosition</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to the [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html).</t>
+    <t>Navigate to [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,6 +94,72 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>5335366</t>
+  </si>
+  <si>
+    <t>LEFT LATERAL RECUMBENT</t>
+  </si>
+  <si>
+    <t>4688663</t>
+  </si>
+  <si>
+    <t>LYING</t>
+  </si>
+  <si>
+    <t>5335362</t>
+  </si>
+  <si>
+    <t>PRONE</t>
+  </si>
+  <si>
+    <t>5335364</t>
+  </si>
+  <si>
+    <t>RIGHT LATERAL RECUMBENT</t>
+  </si>
+  <si>
+    <t>4688682</t>
+  </si>
+  <si>
+    <t>SEMIFOWLERS</t>
+  </si>
+  <si>
+    <t>4688703</t>
+  </si>
+  <si>
+    <t>SITTING</t>
+  </si>
+  <si>
+    <t>4688707</t>
+  </si>
+  <si>
+    <t>STANDING</t>
+  </si>
+  <si>
+    <t>4500643</t>
+  </si>
+  <si>
+    <t>STANDING WEIGHT</t>
+  </si>
+  <si>
+    <t>4688694</t>
+  </si>
+  <si>
+    <t>TRENDELENBURG</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/vistaDefinedElements/120.5-5</t>
   </si>
 </sst>
 </file>
@@ -270,24 +337,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s" s="2">
         <v>12</v>
       </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -347,6 +412,116 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,66 +355,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -430,98 +435,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 120.5-5" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -30,21 +31,18 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>VSVFVitalsPosition</t>
+    <t>VF_VitalsPosition</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>VF_VitalsPosition</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -163,6 +161,57 @@
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedElements/120.5-5</t>
+  </si>
+  <si>
+    <t>102536004</t>
+  </si>
+  <si>
+    <t>Left lateral decubitus position (finding)</t>
+  </si>
+  <si>
+    <t>102538003</t>
+  </si>
+  <si>
+    <t>Recumbent body position (finding)</t>
+  </si>
+  <si>
+    <t>1240000</t>
+  </si>
+  <si>
+    <t>Prone body position (finding)</t>
+  </si>
+  <si>
+    <t>102535000</t>
+  </si>
+  <si>
+    <t>Right lateral decubitus position (finding)</t>
+  </si>
+  <si>
+    <t>426408003</t>
+  </si>
+  <si>
+    <t>Semi-Fowler's position (finding)</t>
+  </si>
+  <si>
+    <t>33586001</t>
+  </si>
+  <si>
+    <t>Sitting position (finding)</t>
+  </si>
+  <si>
+    <t>10904000</t>
+  </si>
+  <si>
+    <t>Orthostatic body position (finding)</t>
+  </si>
+  <si>
+    <t>34106002</t>
+  </si>
+  <si>
+    <t>Trendelenburg position (finding)</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -340,83 +389,83 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -435,79 +484,189 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>46</v>
@@ -518,15 +677,7 @@
         <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from 120.5-5" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from 120.5-5" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html)</t>
+    <t>Navigate to [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html)
+&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,6 +101,63 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>102536004</t>
+  </si>
+  <si>
+    <t>Left lateral decubitus position (finding)</t>
+  </si>
+  <si>
+    <t>102538003</t>
+  </si>
+  <si>
+    <t>Recumbent body position (finding)</t>
+  </si>
+  <si>
+    <t>1240000</t>
+  </si>
+  <si>
+    <t>Prone body position (finding)</t>
+  </si>
+  <si>
+    <t>102535000</t>
+  </si>
+  <si>
+    <t>Right lateral decubitus position (finding)</t>
+  </si>
+  <si>
+    <t>426408003</t>
+  </si>
+  <si>
+    <t>Semi-Fowler's position (finding)</t>
+  </si>
+  <si>
+    <t>33586001</t>
+  </si>
+  <si>
+    <t>Sitting position (finding)</t>
+  </si>
+  <si>
+    <t>10904000</t>
+  </si>
+  <si>
+    <t>Orthostatic body position (finding)</t>
+  </si>
+  <si>
+    <t>34106002</t>
+  </si>
+  <si>
+    <t>Trendelenburg position (finding)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>5335366</t>
   </si>
   <si>
@@ -154,64 +212,7 @@
     <t>TRENDELENBURG</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
     <t>http://va.gov/terminology/vistaDefinedElements/120.5-5</t>
-  </si>
-  <si>
-    <t>102536004</t>
-  </si>
-  <si>
-    <t>Left lateral decubitus position (finding)</t>
-  </si>
-  <si>
-    <t>102538003</t>
-  </si>
-  <si>
-    <t>Recumbent body position (finding)</t>
-  </si>
-  <si>
-    <t>1240000</t>
-  </si>
-  <si>
-    <t>Prone body position (finding)</t>
-  </si>
-  <si>
-    <t>102535000</t>
-  </si>
-  <si>
-    <t>Right lateral decubitus position (finding)</t>
-  </si>
-  <si>
-    <t>426408003</t>
-  </si>
-  <si>
-    <t>Semi-Fowler's position (finding)</t>
-  </si>
-  <si>
-    <t>33586001</t>
-  </si>
-  <si>
-    <t>Sitting position (finding)</t>
-  </si>
-  <si>
-    <t>10904000</t>
-  </si>
-  <si>
-    <t>Orthostatic body position (finding)</t>
-  </si>
-  <si>
-    <t>34106002</t>
-  </si>
-  <si>
-    <t>Trendelenburg position (finding)</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -475,6 +476,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -492,191 +595,89 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
         <v>65</v>
       </c>
     </row>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,10 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_VitalsPosition](ConceptMap-CMVFVitalsPosition.html)
-&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -212,7 +208,7 @@
     <t>TRENDELENBURG</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/120.5-5</t>
+    <t>http://va.gov/terminology/vistaDefinedTerms/120.5-5</t>
   </si>
 </sst>
 </file>
@@ -445,28 +441,26 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +479,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -493,82 +487,82 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -587,7 +581,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -595,90 +589,90 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet for terminology map VF_VitalsPosition</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -441,26 +444,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +484,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -487,82 +492,82 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -581,7 +586,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -589,90 +594,90 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from 120.5-5" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from US Department of" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for terminology map VF_VitalsPosition</t>
+    <t>ValueSet for Terminology Maps VF_VitalsPosition</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -211,7 +211,7 @@
     <t>TRENDELENBURG</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedTerms/120.5-5</t>
+    <t>http://terminology.hl7.org/CodeSystem/VHA</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from US Department of" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -52,13 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for Terminology Maps VF_VitalsPosition</t>
+    <t>FHIR Target ValueSet for Terminology Maps VF_VitalsPosition</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -155,63 +154,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>5335366</t>
-  </si>
-  <si>
-    <t>LEFT LATERAL RECUMBENT</t>
-  </si>
-  <si>
-    <t>4688663</t>
-  </si>
-  <si>
-    <t>LYING</t>
-  </si>
-  <si>
-    <t>5335362</t>
-  </si>
-  <si>
-    <t>PRONE</t>
-  </si>
-  <si>
-    <t>5335364</t>
-  </si>
-  <si>
-    <t>RIGHT LATERAL RECUMBENT</t>
-  </si>
-  <si>
-    <t>4688682</t>
-  </si>
-  <si>
-    <t>SEMIFOWLERS</t>
-  </si>
-  <si>
-    <t>4688703</t>
-  </si>
-  <si>
-    <t>SITTING</t>
-  </si>
-  <si>
-    <t>4688707</t>
-  </si>
-  <si>
-    <t>STANDING</t>
-  </si>
-  <si>
-    <t>4500643</t>
-  </si>
-  <si>
-    <t>STANDING WEIGHT</t>
-  </si>
-  <si>
-    <t>4688694</t>
-  </si>
-  <si>
-    <t>TRENDELENBURG</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/VHA</t>
   </si>
 </sst>
 </file>
@@ -573,114 +515,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsPosition.xlsx
+++ b/docs/ValueSet-VSVFVitalsPosition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
